--- a/output/invoice_info_db/未匹配清单_发票信息_2026_20260621.xlsx
+++ b/output/invoice_info_db/未匹配清单_发票信息_2026_20260621.xlsx
@@ -7310,13 +7310,13 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>39239</v>
+        <v>39258</v>
       </c>
       <c r="C2">
         <v>1150</v>
       </c>
       <c r="D2">
-        <v>40389</v>
+        <v>40408</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
